--- a/outputs/q3/inventory_trace.xlsx
+++ b/outputs/q3/inventory_trace.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>预测可供货量</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>计划发运量</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周转运总能力</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>生产需求产品当量</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>实际到厂产品当量</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>实际库存产品当量</t>
         </is>
@@ -450,10 +470,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>29871.56102358679</v>
+        <v>24057.85695389733</v>
       </c>
       <c r="C2" t="n">
-        <v>58071.56102358679</v>
+        <v>16093.14064867982</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25907.61110522476</v>
+      </c>
+      <c r="G2" t="n">
+        <v>110507.6111052248</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +493,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>29871.56102358679</v>
+        <v>21467.31401669093</v>
       </c>
       <c r="C3" t="n">
-        <v>59743.12204717359</v>
+        <v>15114.09693156079</v>
+      </c>
+      <c r="D3" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F3" t="n">
+        <v>23940.21451648356</v>
+      </c>
+      <c r="G3" t="n">
+        <v>106247.8256217083</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +516,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>29871.56102358679</v>
+        <v>22964.2070308858</v>
       </c>
       <c r="C4" t="n">
-        <v>61414.68307076038</v>
+        <v>15885.67034597833</v>
+      </c>
+      <c r="D4" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F4" t="n">
+        <v>25171.86486153848</v>
+      </c>
+      <c r="G4" t="n">
+        <v>103219.6904832468</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +539,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>29871.56102358679</v>
+        <v>22033.12797437774</v>
       </c>
       <c r="C5" t="n">
-        <v>63086.24409434717</v>
+        <v>15088.29595080277</v>
+      </c>
+      <c r="D5" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23940.14121854525</v>
+      </c>
+      <c r="G5" t="n">
+        <v>98959.83170179203</v>
       </c>
     </row>
     <row r="6">
@@ -494,10 +562,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>29871.56102358679</v>
+        <v>22698.41695046571</v>
       </c>
       <c r="C6" t="n">
-        <v>64757.80511793397</v>
+        <v>15983.97474530101</v>
+      </c>
+      <c r="D6" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F6" t="n">
+        <v>25335.95832135977</v>
+      </c>
+      <c r="G6" t="n">
+        <v>96095.79002315181</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +585,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>29871.56102358679</v>
+        <v>23357.0850002707</v>
       </c>
       <c r="C7" t="n">
-        <v>66429.36614152076</v>
+        <v>17072.02320652604</v>
+      </c>
+      <c r="D7" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F7" t="n">
+        <v>26914.19974187384</v>
+      </c>
+      <c r="G7" t="n">
+        <v>94809.98976502565</v>
       </c>
     </row>
     <row r="8">
@@ -516,10 +608,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>29871.56102358679</v>
+        <v>22262.93772859696</v>
       </c>
       <c r="C8" t="n">
-        <v>68100.92716510755</v>
+        <v>17014.33542164793</v>
+      </c>
+      <c r="D8" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F8" t="n">
+        <v>26723.74421452323</v>
+      </c>
+      <c r="G8" t="n">
+        <v>93333.73397954888</v>
       </c>
     </row>
     <row r="9">
@@ -527,10 +631,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>29871.56102358679</v>
+        <v>22273.23533772141</v>
       </c>
       <c r="C9" t="n">
-        <v>69772.48818869435</v>
+        <v>16990.05538012114</v>
+      </c>
+      <c r="D9" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F9" t="n">
+        <v>26690.86307920013</v>
+      </c>
+      <c r="G9" t="n">
+        <v>91824.59705874902</v>
       </c>
     </row>
     <row r="10">
@@ -538,10 +654,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>29871.56102358679</v>
+        <v>23465.47404499833</v>
       </c>
       <c r="C10" t="n">
-        <v>71444.04921228114</v>
+        <v>17736.32106411578</v>
+      </c>
+      <c r="D10" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F10" t="n">
+        <v>27887.31888600574</v>
+      </c>
+      <c r="G10" t="n">
+        <v>91511.91594475476</v>
       </c>
     </row>
     <row r="11">
@@ -549,10 +677,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>29871.56102358679</v>
+        <v>23788.741021087</v>
       </c>
       <c r="C11" t="n">
-        <v>73115.61023586793</v>
+        <v>17224.36648416666</v>
+      </c>
+      <c r="D11" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F11" t="n">
+        <v>27090.96867914177</v>
+      </c>
+      <c r="G11" t="n">
+        <v>90402.88462389653</v>
       </c>
     </row>
     <row r="12">
@@ -560,10 +700,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>29871.56102358679</v>
+        <v>24374.7773400639</v>
       </c>
       <c r="C12" t="n">
-        <v>74787.17125945473</v>
+        <v>17863.18131896285</v>
+      </c>
+      <c r="D12" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F12" t="n">
+        <v>28092.01179689498</v>
+      </c>
+      <c r="G12" t="n">
+        <v>90294.89642079151</v>
       </c>
     </row>
     <row r="13">
@@ -571,10 +723,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>29871.56102358679</v>
+        <v>23974.45079810757</v>
       </c>
       <c r="C13" t="n">
-        <v>76458.73228304152</v>
+        <v>17627.14474988295</v>
+      </c>
+      <c r="D13" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F13" t="n">
+        <v>27720.80173358958</v>
+      </c>
+      <c r="G13" t="n">
+        <v>89815.6981543811</v>
       </c>
     </row>
     <row r="14">
@@ -582,10 +746,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>29871.56102358679</v>
+        <v>24487.1276408816</v>
       </c>
       <c r="C14" t="n">
-        <v>78130.29330662831</v>
+        <v>18365.29856810344</v>
+      </c>
+      <c r="D14" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F14" t="n">
+        <v>28895.14623663562</v>
+      </c>
+      <c r="G14" t="n">
+        <v>90510.84439101671</v>
       </c>
     </row>
     <row r="15">
@@ -593,10 +769,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>29871.56102358679</v>
+        <v>25279.39919690178</v>
       </c>
       <c r="C15" t="n">
-        <v>79801.85433021511</v>
+        <v>18703.68688780855</v>
+      </c>
+      <c r="D15" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F15" t="n">
+        <v>29369.10749812465</v>
+      </c>
+      <c r="G15" t="n">
+        <v>91679.95188914136</v>
       </c>
     </row>
     <row r="16">
@@ -604,10 +792,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>29871.56102358679</v>
+        <v>24277.96367623252</v>
       </c>
       <c r="C16" t="n">
-        <v>81473.4153538019</v>
+        <v>17971.01506796203</v>
+      </c>
+      <c r="D16" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F16" t="n">
+        <v>28268.14055599799</v>
+      </c>
+      <c r="G16" t="n">
+        <v>91748.09244513935</v>
       </c>
     </row>
     <row r="17">
@@ -615,10 +815,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>29871.56102358679</v>
+        <v>23426.14399949757</v>
       </c>
       <c r="C17" t="n">
-        <v>83144.9763773887</v>
+        <v>17247.50953802207</v>
+      </c>
+      <c r="D17" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F17" t="n">
+        <v>27108.41536029042</v>
+      </c>
+      <c r="G17" t="n">
+        <v>90656.50780542976</v>
       </c>
     </row>
     <row r="18">
@@ -626,10 +838,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>29871.56102358679</v>
+        <v>23672.98873977517</v>
       </c>
       <c r="C18" t="n">
-        <v>84816.53740097549</v>
+        <v>17748.48976745667</v>
+      </c>
+      <c r="D18" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F18" t="n">
+        <v>27934.2120534674</v>
+      </c>
+      <c r="G18" t="n">
+        <v>90390.71985889717</v>
       </c>
     </row>
     <row r="19">
@@ -637,10 +861,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>29871.56102358679</v>
+        <v>25289.55944220957</v>
       </c>
       <c r="C19" t="n">
-        <v>86488.09842456228</v>
+        <v>19373.92418746005</v>
+      </c>
+      <c r="D19" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F19" t="n">
+        <v>30542.82968354447</v>
+      </c>
+      <c r="G19" t="n">
+        <v>92733.54954244163</v>
       </c>
     </row>
     <row r="20">
@@ -648,10 +884,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>29871.56102358679</v>
+        <v>24311.8499523088</v>
       </c>
       <c r="C20" t="n">
-        <v>88159.65944814908</v>
+        <v>18604.99226031199</v>
+      </c>
+      <c r="D20" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F20" t="n">
+        <v>29287.48392035474</v>
+      </c>
+      <c r="G20" t="n">
+        <v>93821.03346279637</v>
       </c>
     </row>
     <row r="21">
@@ -659,10 +907,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>29871.56102358679</v>
+        <v>23071.81683196064</v>
       </c>
       <c r="C21" t="n">
-        <v>89831.22047173587</v>
+        <v>17541.21378575918</v>
+      </c>
+      <c r="D21" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F21" t="n">
+        <v>27613.03796167772</v>
+      </c>
+      <c r="G21" t="n">
+        <v>93234.0714244741</v>
       </c>
     </row>
     <row r="22">
@@ -670,10 +930,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>29871.56102358679</v>
+        <v>24654.66128980251</v>
       </c>
       <c r="C22" t="n">
-        <v>91502.78149532266</v>
+        <v>18349.55628448253</v>
+      </c>
+      <c r="D22" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F22" t="n">
+        <v>28898.69849327786</v>
+      </c>
+      <c r="G22" t="n">
+        <v>93932.76991775195</v>
       </c>
     </row>
     <row r="23">
@@ -681,10 +953,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>29871.56102358679</v>
+        <v>23970.55278523027</v>
       </c>
       <c r="C23" t="n">
-        <v>93174.34251890946</v>
+        <v>17836.22755852674</v>
+      </c>
+      <c r="D23" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F23" t="n">
+        <v>28069.46722648219</v>
+      </c>
+      <c r="G23" t="n">
+        <v>93802.23714423414</v>
       </c>
     </row>
     <row r="24">
@@ -692,10 +976,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>29871.56102358679</v>
+        <v>23192.32767614599</v>
       </c>
       <c r="C24" t="n">
-        <v>94845.90354249625</v>
+        <v>17804.49372440573</v>
+      </c>
+      <c r="D24" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F24" t="n">
+        <v>28026.10583050711</v>
+      </c>
+      <c r="G24" t="n">
+        <v>93628.34297474124</v>
       </c>
     </row>
     <row r="25">
@@ -703,10 +999,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>29871.56102358679</v>
+        <v>23266.87621504927</v>
       </c>
       <c r="C25" t="n">
-        <v>96517.46456608304</v>
+        <v>17712.20992644556</v>
+      </c>
+      <c r="D25" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>28200</v>
+      </c>
+      <c r="F25" t="n">
+        <v>27839.26723600729</v>
+      </c>
+      <c r="G25" t="n">
+        <v>93267.61021074853</v>
       </c>
     </row>
   </sheetData>
